--- a/locations.xlsx
+++ b/locations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdbfade8bf3b2706/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77A58505-5984-44D1-BC0D-EF2AC13D7F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{77A58505-5984-44D1-BC0D-EF2AC13D7F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34E47DD3-7C53-4549-A80A-30B71E483604}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{619B4F3F-9598-4443-804E-4137D8546EF0}"/>
   </bookViews>
@@ -36,37 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>"Cities" :</t>
-  </si>
-  <si>
-    <t>"Boston",</t>
-  </si>
-  <si>
-    <t>"Chicago",</t>
-  </si>
-  <si>
-    <t>"Houston",</t>
-  </si>
-  <si>
-    <t>"Los Angeles",</t>
-  </si>
-  <si>
-    <t>"Miami",</t>
-  </si>
-  <si>
-    <t>"New York",</t>
-  </si>
-  <si>
-    <t>"San Francisco",</t>
-  </si>
-  <si>
-    <t>"Seattle"</t>
-  </si>
-  <si>
-    <t>"Latitude" :</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>42°21′37″N</t>
   </si>
@@ -92,9 +62,6 @@
     <t>47°36′14″N</t>
   </si>
   <si>
-    <t>"Longitude" :</t>
-  </si>
-  <si>
     <t>71°3′28″W</t>
   </si>
   <si>
@@ -119,7 +86,37 @@
     <t>122°19′48″W</t>
   </si>
   <si>
-    <t>"Count" :</t>
+    <t>Cities</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>Seattle</t>
   </si>
 </sst>
 </file>
@@ -143,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,233 +163,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -403,19 +185,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{85996A70-5FE9-4E71-82CD-96A1D411DE97}" name="Table1" displayName="Table1" ref="A1:D9" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:D9" xr:uid="{85996A70-5FE9-4E71-82CD-96A1D411DE97}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D135B364-0A00-4B52-8FC0-3A0C64440147}" name="&quot;Cities&quot; :" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{EA73075B-E134-4F67-9CA5-ED2B0CE3780A}" name="&quot;Latitude&quot; :" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{0509C9A4-7EB9-4375-94A6-E74DDE462CCD}" name="&quot;Longitude&quot; :" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{0A684657-C3B2-449A-A348-E69F531E6E56}" name="&quot;Count&quot; :" dataDxfId="1"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -735,145 +504,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5845D1F9-67BA-4721-9930-AC569E62D54D}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="9">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>